--- a/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Buôn Kuop 1977_2026.xlsx
+++ b/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Buôn Kuop 1977_2026.xlsx
@@ -5945,7 +5945,7 @@
         <v>159.874</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>83.5827994</v>
+        <v>135.6781879</v>
       </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
@@ -5979,7 +5979,7 @@
         <v>272.60000000000002</v>
       </c>
       <c r="Z52" s="6" t="n">
-        <v>332.23</v>
+        <v>331.03</v>
       </c>
     </row>
     <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
